--- a/src/main/resources/Registration_Field_Values.xlsx
+++ b/src/main/resources/Registration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68E065B-9CBB-4A94-A3CD-8000BB516A44}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF40F233-AB88-444B-8983-B6AF83B55CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{4CE601B7-22FC-4039-9F2A-7CEEA63A282D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CE601B7-22FC-4039-9F2A-7CEEA63A282D}"/>
   </bookViews>
   <sheets>
     <sheet name="smeReviewerRegistration" sheetId="1" r:id="rId1"/>
@@ -47,30 +47,12 @@
     <t>None</t>
   </si>
   <si>
-    <t>fieldSalutation</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
-    <t>fieldFirstName</t>
-  </si>
-  <si>
-    <t>fieldLastName</t>
-  </si>
-  <si>
-    <t>fieldPhone</t>
-  </si>
-  <si>
-    <t>fieldEmail</t>
-  </si>
-  <si>
     <t>smeReviewer@yopmail.com</t>
   </si>
   <si>
-    <t>fieldAffiliatedInstitution__c</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
@@ -78,13 +60,31 @@
   </si>
   <si>
     <t>Automation Runtime Contact</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>AffiliatedInstitution__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +105,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,13 +134,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -451,14 +458,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8139253-FD8E-4CA8-8249-508BE7CAC2F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,70 +476,70 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>9876543210</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Registration_Field_Values.xlsx
+++ b/src/main/resources/Registration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF40F233-AB88-444B-8983-B6AF83B55CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3062FB23-8F27-46F0-A5EE-C14D8C15DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CE601B7-22FC-4039-9F2A-7CEEA63A282D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4CE601B7-22FC-4039-9F2A-7CEEA63A282D}"/>
   </bookViews>
   <sheets>
     <sheet name="smeReviewerRegistration" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,24 +93,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -132,16 +120,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -161,9 +147,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -201,7 +187,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -307,7 +293,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -449,7 +435,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -458,14 +444,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8139253-FD8E-4CA8-8249-508BE7CAC2F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,66 +462,66 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>9876543210</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">

--- a/src/main/resources/Registration_Field_Values.xlsx
+++ b/src/main/resources/Registration_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3062FB23-8F27-46F0-A5EE-C14D8C15DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE119B01-F9F2-4CD4-B55B-FBC48CF1D95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4CE601B7-22FC-4039-9F2A-7CEEA63A282D}"/>
   </bookViews>
